--- a/AtchisonRegime/Outputs/USA/USA_Size_Tilt/df_regTrendSummaryUSA_Size_Tilt.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA_Size_Tilt/df_regTrendSummaryUSA_Size_Tilt.xlsx
@@ -758,13 +758,13 @@
         <v>45138</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3297869389997989</v>
+        <v>0.2170720470303835</v>
       </c>
     </row>
   </sheetData>
